--- a/Convert_from_xlsx_to_Json/table_normalization/food-table10.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/food-table10.xlsx
@@ -293,10 +293,10 @@
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
